--- a/astro-site/public/dl/guia-restaurante-mexicano/escandallo-maestro-mexicano.xlsx
+++ b/astro-site/public/dl/guia-restaurante-mexicano/escandallo-maestro-mexicano.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escandallo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Escandallo'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -522,9 +524,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -544,6 +546,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -572,10 +575,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-mexicano · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -584,7 +596,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -593,7 +614,7 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -621,6 +642,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -688,14 +710,14 @@
       </c>
       <c r="E6" s="12">
         <f>(C6/1000)*D6</f>
-        <v/>
+        <v>0.27</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>0.02</v>
       </c>
       <c r="G6" s="12">
         <f>E6*(1+F6)</f>
-        <v/>
+        <v>0.27540000000000003</v>
       </c>
     </row>
     <row r="7">
@@ -715,14 +737,14 @@
       </c>
       <c r="E7" s="12">
         <f>(C7/1000)*D7</f>
-        <v/>
+        <v>1.53</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>0.08</v>
       </c>
       <c r="G7" s="12">
         <f>E7*(1+F7)</f>
-        <v/>
+        <v>1.6524</v>
       </c>
     </row>
     <row r="8">
@@ -742,14 +764,14 @@
       </c>
       <c r="E8" s="12">
         <f>(C8/1000)*D8</f>
-        <v/>
+        <v>0.08</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="G8" s="12">
         <f>E8*(1+F8)</f>
-        <v/>
+        <v>0.092</v>
       </c>
     </row>
     <row r="9">
@@ -769,14 +791,14 @@
       </c>
       <c r="E9" s="12">
         <f>(C9/1000)*D9</f>
-        <v/>
+        <v>0.03</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>0.1</v>
       </c>
       <c r="G9" s="12">
         <f>E9*(1+F9)</f>
-        <v/>
+        <v>0.033</v>
       </c>
     </row>
     <row r="10">
@@ -796,14 +818,14 @@
       </c>
       <c r="E10" s="12">
         <f>(C10/1000)*D10</f>
-        <v/>
+        <v>0.06</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="G10" s="12">
         <f>E10*(1+F10)</f>
-        <v/>
+        <v>0.072</v>
       </c>
     </row>
     <row r="11">
@@ -823,14 +845,14 @@
       </c>
       <c r="E11" s="12">
         <f>(C11/1000)*D11</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="G11" s="12">
         <f>E11*(1+F11)</f>
-        <v/>
+        <v>0.058499999999999996</v>
       </c>
     </row>
     <row r="12">
@@ -850,14 +872,14 @@
       </c>
       <c r="E12" s="12">
         <f>(C12/1000)*D12</f>
-        <v/>
+        <v>0.09</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="12">
         <f>E12*(1+F12)</f>
-        <v/>
+        <v>0.09</v>
       </c>
     </row>
     <row r="13">
@@ -877,14 +899,14 @@
       </c>
       <c r="E13" s="12">
         <f>(C13/1000)*D13</f>
-        <v/>
+        <v>0.045</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="12">
         <f>E13*(1+F13)</f>
-        <v/>
+        <v>0.045</v>
       </c>
     </row>
     <row r="14">
@@ -904,16 +926,17 @@
       </c>
       <c r="E14" s="12">
         <f>(C14/1000)*D14</f>
-        <v/>
+        <v>0.12</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="12">
         <f>E14*(1+F14)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -922,7 +945,7 @@
       </c>
       <c r="G16" s="14">
         <f>SUM(G6:G14)</f>
-        <v/>
+        <v>2.4383</v>
       </c>
     </row>
     <row r="17">
@@ -933,7 +956,7 @@
       </c>
       <c r="G17" s="12">
         <f>G16/0.30</f>
-        <v/>
+        <v>8.127666666666666</v>
       </c>
     </row>
     <row r="18">
@@ -944,9 +967,10 @@
       </c>
       <c r="G18" s="12">
         <f>G17*1.10</f>
-        <v/>
-      </c>
-    </row>
+        <v>8.940433333333333</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
@@ -960,6 +984,15 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>